--- a/agent_runs/manjidiwang/episodes/ep12/storyboard_index.xlsx
+++ b/agent_runs/manjidiwang/episodes/ep12/storyboard_index.xlsx
@@ -84,7 +84,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>特护病房暗处截杀（，总时长：15秒，镜头数：7个）</t>
+          <t>特护病房暗处截杀</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -132,7 +132,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>病床前制服杀手（，总时长：13秒，镜头数：5个）</t>
+          <t>病床前制服杀手</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -180,7 +180,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>撞晕后的诱饵放话（，总时长：11秒，镜头数：4个）</t>
+          <t>撞晕后的诱饵放话</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -228,7 +228,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>安保办公室放出诱饵（，总时长：10秒，镜头数：4个）</t>
+          <t>安保办公室放出诱饵</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -276,7 +276,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>机房灯亮钓出内鬼（，总时长：12秒，镜头数：5个）</t>
+          <t>机房灯亮钓出内鬼</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -324,7 +324,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>供出总裁威胁（，总时长：10秒，镜头数：4个）</t>
+          <t>供出总裁威胁</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
